--- a/schema.xlsx
+++ b/schema.xlsx
@@ -191,94 +191,114 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>Group, Subgroup, Student group</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Group, Staff group, Student group, Subgroup</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Room, Location</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t/>
+          <t>Activity</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Anledning</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Person</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>Länk</t>
-        </is>
-      </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>Programme</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
           <t>Study instructions</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>Person Group</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>w4</t>
+          <t>w52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Julafton</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -293,7 +313,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t/>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -303,12 +323,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t/>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -332,6 +352,24 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -340,37 +378,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>w4</t>
+          <t>w52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Juldagen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -385,7 +423,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -395,12 +433,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Lecture, Seminar</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -424,6 +462,24 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -432,37 +488,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>w4</t>
+          <t>w52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Annandag jul</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -477,7 +533,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.027 Hökeberget</t>
+          <t/>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -487,12 +543,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t/>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -516,6 +572,24 @@
         </is>
       </c>
       <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -524,7 +598,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>w4</t>
+          <t>w1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -534,27 +608,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Nyårsafton</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -594,7 +668,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>ALARM</t>
+          <t/>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -608,6 +682,24 @@
         </is>
       </c>
       <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -616,37 +708,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>w5</t>
+          <t>w1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Nyårsdagen</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -661,7 +753,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t/>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -671,12 +763,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t/>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -700,6 +792,24 @@
         </is>
       </c>
       <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -708,37 +818,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>w5</t>
+          <t>w2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Trettondedag jul</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -753,7 +863,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t/>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -763,12 +873,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Computer training</t>
+          <t/>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -792,6 +902,24 @@
         </is>
       </c>
       <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -800,27 +928,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>w5</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -845,22 +973,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.032 Bulleråsen</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Lecture, Group work</t>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -883,7 +1011,23 @@
           <t/>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -892,17 +1036,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>w5</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -912,12 +1056,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -942,17 +1086,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture, Seminar</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -962,7 +1106,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Recommended Task to prepare for examination seminar 2026-02-02</t>
+          <t/>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -975,7 +1119,23 @@
           <t/>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -984,17 +1144,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>w6</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1004,7 +1164,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,22 +1189,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>3.027 Hökeberget</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Lecture, Compulsory, Seminar</t>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1054,12 +1214,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Mandatory between 10:15-15:00</t>
+          <t/>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t/>
+          <t>NOTE! Lecture is 9.15-11</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1067,7 +1227,23 @@
           <t/>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1076,32 +1252,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>w6</t>
+          <t>w4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1121,7 +1297,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.040A Lilla Änggården ALC</t>
+          <t/>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1131,12 +1307,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Compulsory, Seminar</t>
+          <t/>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1146,12 +1322,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Mandatory between 10:15-15:00</t>
+          <t/>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t/>
+          <t>ALARM</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1159,7 +1335,23 @@
           <t/>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1168,17 +1360,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w6</t>
+          <t>w5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1188,7 +1380,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1213,22 +1405,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1412, Medg 11</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1251,7 +1443,23 @@
           <t/>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1260,7 +1468,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>w7</t>
+          <t>w5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1270,22 +1478,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1310,17 +1518,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1343,7 +1551,23 @@
           <t/>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1352,32 +1576,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>w7</t>
+          <t>w5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1397,22 +1621,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>3.032 Bulleråsen</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture, Group work</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Computer training</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1435,7 +1659,23 @@
           <t/>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1444,7 +1684,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>w7</t>
+          <t>w5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,22 +1694,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1494,17 +1734,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t/>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1519,7 +1759,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t/>
+          <t>Recommended Task to prepare for examination seminar 2026-02-02</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1527,7 +1767,23 @@
           <t/>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1536,32 +1792,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>w7</t>
+          <t>w6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1586,17 +1842,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture, Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1611,7 +1867,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t/>
+          <t>Mandatory between 10:15-15:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1619,7 +1875,23 @@
           <t/>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1628,7 +1900,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>w8</t>
+          <t>w6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1638,22 +1910,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1673,22 +1945,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>3.040A Lilla Änggården ALC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1703,7 +1975,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t/>
+          <t>Mandatory between 10:15-15:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1711,7 +1983,23 @@
           <t/>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1720,32 +2008,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>w8</t>
+          <t>w6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1765,22 +2053,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>1412, Medg 11</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1790,7 +2078,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Recommended Computer session to prepare for seminar 2026-02-18</t>
+          <t/>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1803,7 +2091,23 @@
           <t/>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1812,17 +2116,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>w8</t>
+          <t>w7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1832,7 +2136,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1862,17 +2166,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Compulsory, Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1882,7 +2186,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Mandatory between 10:15-15:00</t>
+          <t/>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1895,7 +2199,23 @@
           <t/>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1904,17 +2224,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>w8</t>
+          <t>w7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1924,12 +2244,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1954,17 +2274,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Compulsory, Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +2294,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mandatory between 10:15-15:00</t>
+          <t/>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1987,7 +2307,23 @@
           <t/>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1996,27 +2332,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>w9</t>
+          <t>w7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2046,17 +2382,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2066,7 +2402,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Repetition</t>
+          <t/>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2079,7 +2415,23 @@
           <t/>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2088,17 +2440,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>w9</t>
+          <t>w7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2108,12 +2460,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2138,17 +2490,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t/>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Computer training</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2171,7 +2523,23 @@
           <t/>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2180,27 +2548,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>w9</t>
+          <t>w8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2230,17 +2598,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2263,7 +2631,23 @@
           <t/>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2272,17 +2656,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>w9</t>
+          <t>w8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2292,12 +2676,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2317,22 +2701,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.040B Skäleberget</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t/>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Compulsory, Seminar</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2347,7 +2731,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t/>
+          <t>Recommended Computer session to prepare for seminar 2026-02-18</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2355,7 +2739,23 @@
           <t/>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2364,17 +2764,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>w10</t>
+          <t>w8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2384,7 +2784,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2414,17 +2814,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Question time, Rehearsal</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2434,12 +2834,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Repetion on Annas material</t>
+          <t/>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t/>
+          <t>Mandatory between 10:15-15:00</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2447,7 +2847,23 @@
           <t/>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2456,17 +2872,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>w10</t>
+          <t>w8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2476,7 +2892,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2506,17 +2922,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman</t>
+          <t/>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Question time</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2526,12 +2942,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Questions and discussion</t>
+          <t/>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t/>
+          <t>Mandatory between 10:15-15:00</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2539,7 +2955,23 @@
           <t/>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2548,17 +2980,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>w10</t>
+          <t>w9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2568,7 +3000,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2593,24 +3025,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1412, Medg 11</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t/>
@@ -2631,7 +3063,23 @@
           <t/>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2640,17 +3088,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>w10</t>
+          <t>w9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2660,7 +3108,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2685,24 +3133,24 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1412, Medg 11</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Compulsory, Computer training</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t/>
@@ -2723,7 +3171,23 @@
           <t/>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2732,17 +3196,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>w11</t>
+          <t>w9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2752,7 +3216,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2782,19 +3246,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t/>
@@ -2815,7 +3279,23 @@
           <t/>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2824,17 +3304,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>w11</t>
+          <t>w9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2844,7 +3324,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2869,24 +3349,24 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>3.040B Skäleberget</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Compulsory, Computer training</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t/>
@@ -2907,7 +3387,23 @@
           <t/>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2916,32 +3412,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>w11</t>
+          <t>w10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2961,22 +3457,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3.040B Skäleberget</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t/>
+          <t>Question time, Rehearsal</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2991,7 +3487,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t/>
+          <t>Repetion on Annas material</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2999,7 +3495,23 @@
           <t/>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3008,32 +3520,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>w11</t>
+          <t>w10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3053,22 +3565,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1412, Medg 11</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t/>
+          <t>Question time</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Compulsory, Computer training</t>
+          <t>Anna Grimby-Ekman</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3083,7 +3595,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t/>
+          <t>Questions and discussion</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3091,7 +3603,23 @@
           <t/>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3100,17 +3628,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>w12</t>
+          <t>w10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3120,7 +3648,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3145,24 +3673,24 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>1412, Medg 11</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t/>
@@ -3183,7 +3711,23 @@
           <t/>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3192,17 +3736,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>w12</t>
+          <t>w10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3212,7 +3756,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3237,24 +3781,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3.029 Blomsteråsen</t>
+          <t>1412, Medg 11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Computer training</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Computer training</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t/>
@@ -3275,7 +3819,23 @@
           <t/>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3284,17 +3844,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>w12</t>
+          <t>w11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3304,7 +3864,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3334,19 +3894,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Lecture</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t/>
@@ -3367,7 +3927,23 @@
           <t/>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3376,17 +3952,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>w12</t>
+          <t>w11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3396,7 +3972,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3421,24 +3997,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1412, Medg 11</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Computer training</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Computer training</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t/>
@@ -3459,7 +4035,23 @@
           <t/>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3468,32 +4060,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>w13</t>
+          <t>w11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3513,22 +4105,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3.032 Bulleråsen</t>
+          <t>3.040B Skäleberget</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Lecture</t>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3538,7 +4130,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Repetition, Q&amp;A</t>
+          <t/>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3551,7 +4143,23 @@
           <t/>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3560,32 +4168,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>w13</t>
+          <t>w11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3605,24 +4213,24 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3.040A Lilla Änggården ALC</t>
+          <t>1412, Medg 11</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>Erik Bülow</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Compulsory, Seminar</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t/>
@@ -3630,7 +4238,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Mandatory for group 1: 13.15-14.30 and group 2: 14.45-16.00</t>
+          <t/>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3643,7 +4251,23 @@
           <t/>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3652,32 +4276,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>w13</t>
+          <t>w12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3697,22 +4321,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Reutersgatan 2C</t>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Digital Exam</t>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3735,7 +4359,23 @@
           <t/>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3744,37 +4384,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>w14</t>
+          <t>w12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Långfredag</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3789,12 +4429,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t/>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3804,7 +4444,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t/>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3827,7 +4467,23 @@
           <t/>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3836,37 +4492,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>w14</t>
+          <t>w12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Påskafton</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3881,12 +4537,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t/>
+          <t>3.029 Blomsteråsen</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3896,7 +4552,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t/>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3919,7 +4575,23 @@
           <t/>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3928,37 +4600,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>w14</t>
+          <t>w12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Påskdagen</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3973,12 +4645,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t/>
+          <t>1412, Medg 11</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t/>
+          <t>Computer training</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3988,7 +4660,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4011,7 +4683,23 @@
           <t/>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4020,7 +4708,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>w15</t>
+          <t>w13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4030,27 +4718,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Annandag påsk</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4065,12 +4753,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t/>
+          <t>3.032 Bulleråsen</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t/>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4080,7 +4768,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t/>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4095,7 +4783,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t/>
+          <t>Repetition, Q&amp;A</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4103,7 +4791,23 @@
           <t/>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4112,37 +4816,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>w16</t>
+          <t>w13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Högskoleprovet</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4157,12 +4861,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t/>
+          <t>3.040A Lilla Änggården ALC</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t/>
+          <t>Compulsory, Seminar</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4172,7 +4876,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t/>
+          <t>Erik Bülow</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4187,7 +4891,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t/>
+          <t>Mandatory for group 1: 13.15-14.30 and group 2: 14.45-16.00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4195,7 +4899,23 @@
           <t/>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4204,37 +4924,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>w18</t>
+          <t>w13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Första maj</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4249,12 +4969,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t/>
+          <t>Reutersgatan 2C</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t/>
+          <t>Digital Exam</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4264,7 +4984,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t/>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4287,7 +5007,23 @@
           <t/>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4296,37 +5032,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>w19</t>
+          <t>w14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>STA220. Health data and questionnaires</t>
+          <t>Långfredag</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4351,12 +5087,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Anna Grimby Ekman, Erik Bülow</t>
+          <t/>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Retake</t>
+          <t/>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4380,6 +5116,24 @@
         </is>
       </c>
       <c r="R47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4388,17 +5142,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>w20</t>
+          <t>w14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4408,7 +5162,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4418,7 +5172,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kristi himmelsfärdsdag</t>
+          <t>Påskafton</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4472,6 +5226,24 @@
         </is>
       </c>
       <c r="R48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4480,17 +5252,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>w21</t>
+          <t>w14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4500,7 +5272,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4510,7 +5282,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pingstafton</t>
+          <t>Påskdagen</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4564,6 +5336,24 @@
         </is>
       </c>
       <c r="R49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4572,17 +5362,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>w21</t>
+          <t>w15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4592,7 +5382,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4602,7 +5392,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pingstdagen</t>
+          <t>Annandag påsk</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4656,6 +5446,24 @@
         </is>
       </c>
       <c r="R50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4664,7 +5472,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>w23</t>
+          <t>w16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4674,27 +5482,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sveriges nationaldag</t>
+          <t>Högskoleprovet</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4748,6 +5556,24 @@
         </is>
       </c>
       <c r="R51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4756,7 +5582,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>w25</t>
+          <t>w18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4766,7 +5592,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4776,7 +5602,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4786,7 +5612,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Midsommarafton</t>
+          <t>Första maj</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4840,6 +5666,24 @@
         </is>
       </c>
       <c r="R52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4848,7 +5692,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>w25</t>
+          <t>w19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4858,27 +5702,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Midsommardagen</t>
+          <t>STA220. Health data and questionnaires</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4898,7 +5742,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t/>
+          <t>Retake</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4908,7 +5752,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t/>
+          <t>Anna Grimby-Ekman, Erik Bülow</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4931,15 +5775,361 @@
           <t/>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>w20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Kristi himmelsfärdsdag</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>w21</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pingstafton</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>w21</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pingstdagen</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
 </row>
-    <row r="55">
+    <row r="58">
 </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
